--- a/摊位申请/摊位申请表统计.xlsx
+++ b/摊位申请/摊位申请表统计.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -633,7 +633,7 @@
           <t>奖品由班级自筹，已备齐</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="n"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-101.docx</t>
@@ -711,7 +711,7 @@
           <t>彩纸等材料已备齐</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-102.docx</t>
@@ -789,7 +789,7 @@
           <t>谜面内容已请语文组老师审定</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-103.docx</t>
@@ -867,7 +867,7 @@
           <t>食品安全承诺书随表附上</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-104.docx</t>
@@ -945,7 +945,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-201.docx</t>
@@ -1023,7 +1023,7 @@
           <t>彩绘颜料为水性安全材质</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-202.docx</t>
@@ -1101,7 +1101,7 @@
           <t>食品安全承诺书随表附上</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-203.docx</t>
@@ -1179,7 +1179,7 @@
           <t>拼图图案为校庆主题定制</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-204.docx</t>
@@ -1257,7 +1257,7 @@
           <t>艺人由班级邀请并已报备筹备组</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-301.docx</t>
@@ -1335,7 +1335,7 @@
           <t>需准备笔墨纸砚若干</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="n"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-302.docx</t>
@@ -1413,7 +1413,7 @@
           <t>认购价格现场公示</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-303.docx</t>
@@ -1491,7 +1491,7 @@
           <t>沙包与地垫向体育组借用</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-304.docx</t>
@@ -1569,7 +1569,7 @@
           <t>题库已请档案室老师审定</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-401.docx</t>
@@ -1647,7 +1647,7 @@
           <t>盲盒礼品已采购完毕</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="n"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-402.docx</t>
@@ -1725,10 +1725,88 @@
           <t>老照片由学校档案室提供</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
           <t>摊位申请表-403.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>CB-2026-016</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026年9月4日</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>四年级（4）班</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>暖心关东煮</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>美食品尝</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>陈老师</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>138-0000-0016</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>chenlaoshi@example.com</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>现场烹煮关东煮，供应萝卜、丸子、豆干等食材，小杯分装方便边逛边吃，汤底清淡少盐，为秋日游园会添一份暖意。</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>桌 3 张、椅 6 张</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>6 人</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>电煮锅×2（各约 800W）</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>食品安全承诺书随表附上；食材当日现购</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>摊位申请表-404.docx</t>
         </is>
       </c>
     </row>
